--- a/Periubran-Rural pond wildlife manuscript data.xlsx
+++ b/Periubran-Rural pond wildlife manuscript data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\S2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\C4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EB17B1-8AD4-4265-9A99-AC82DCCB78F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D1C7B8-A1B6-4DEB-B866-FC0617BFDB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-740" windowWidth="25640" windowHeight="15700" activeTab="1" xr2:uid="{349A57F0-675A-4295-BAB1-3FD8423AC1F0}"/>
+    <workbookView xWindow="-20" yWindow="-740" windowWidth="19020" windowHeight="11370" xr2:uid="{349A57F0-675A-4295-BAB1-3FD8423AC1F0}"/>
   </bookViews>
   <sheets>
     <sheet name="summary table" sheetId="1" r:id="rId1"/>
@@ -212,9 +212,6 @@
     </r>
   </si>
   <si>
-    <t>SINI</t>
-  </si>
-  <si>
     <r>
       <t>Feral Pig (</t>
     </r>
@@ -605,6 +602,390 @@
     <t>BULI</t>
   </si>
   <si>
+    <t>COAT</t>
+  </si>
+  <si>
+    <r>
+      <t>Turkey Vulture (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cathartes aura</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>CAAU</t>
+  </si>
+  <si>
+    <r>
+      <t>Crested Caracara (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Caracara cheriway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>CACH</t>
+  </si>
+  <si>
+    <r>
+      <t>Swainson's Hawk (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Buteo swainsoni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>BUSW</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Snowy Egret </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Egretta thula)</t>
+    </r>
+  </si>
+  <si>
+    <t>Wading Birds &amp; Waterfowl</t>
+  </si>
+  <si>
+    <t>EGTH</t>
+  </si>
+  <si>
+    <r>
+      <t>Cattle Egret (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Bulbucus ibis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Great Blue Heron (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ardea herodias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>ARHE</t>
+  </si>
+  <si>
+    <r>
+      <t>Great Egret (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ardea alba</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>ARAL</t>
+  </si>
+  <si>
+    <r>
+      <t>Little Blue Heron (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Egretta caerulea</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>EGCA</t>
+  </si>
+  <si>
+    <r>
+      <t>Yellow-crowned Night Heron (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Nuctanassa violacea</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>NUVI</t>
+  </si>
+  <si>
+    <r>
+      <t>Black-bellied Whislting Duck (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Denrocyga autumnalis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>DEAU</t>
+  </si>
+  <si>
+    <r>
+      <t>Killdeer (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Charadrius vociferus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ground and Open-Country</t>
+  </si>
+  <si>
+    <t>CHVO</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Greater Roadrunner </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Geococcyx californianus)</t>
+    </r>
+  </si>
+  <si>
+    <t>GECA</t>
+  </si>
+  <si>
+    <r>
+      <t>Wild Turkey (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Meleagris gallopavo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>MEGA</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Ecogroup</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Pond</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>mammal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predator </t>
+  </si>
+  <si>
+    <t>PU</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Small Herbivore</t>
+  </si>
+  <si>
+    <t>Omivore</t>
+  </si>
+  <si>
+    <t>reptile</t>
+  </si>
+  <si>
+    <t>Herbivore</t>
+  </si>
+  <si>
+    <t>Omnivore</t>
+  </si>
+  <si>
+    <t>SCNI</t>
+  </si>
+  <si>
     <r>
       <t>Black Vulture (</t>
     </r>
@@ -616,7 +997,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>Cpragyps atratus</t>
+      <t>Coragyps atratus</t>
     </r>
     <r>
       <rPr>
@@ -629,388 +1010,7 @@
     </r>
   </si>
   <si>
-    <t>COAT</t>
-  </si>
-  <si>
-    <r>
-      <t>Turkey Vulture (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cathartes aura</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>CAAU</t>
-  </si>
-  <si>
-    <r>
-      <t>Crested Caracara (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Caracara cheriway</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>CACH</t>
-  </si>
-  <si>
-    <r>
-      <t>Swainson's Hawk (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Buteo swainsoni</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>BUSW</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Snowy Egret </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(Egretta thula)</t>
-    </r>
-  </si>
-  <si>
-    <t>Wading Birds &amp; Waterfowl</t>
-  </si>
-  <si>
-    <t>EGTH</t>
-  </si>
-  <si>
-    <r>
-      <t>Cattle Egret (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Bulbucus ibis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>BUIS</t>
-  </si>
-  <si>
-    <r>
-      <t>Great Blue Heron (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ardea herodias</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>ARHE</t>
-  </si>
-  <si>
-    <r>
-      <t>Great Egret (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ardea alba</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>ARAL</t>
-  </si>
-  <si>
-    <r>
-      <t>Little Blue Heron (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Egretta caerulea</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>EGCA</t>
-  </si>
-  <si>
-    <r>
-      <t>Yellow-crowned Night Heron (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Nuctanassa violacea</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>NUVI</t>
-  </si>
-  <si>
-    <r>
-      <t>Black-bellied Whislting Duck (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Denrocyga autumnalis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>DEAU</t>
-  </si>
-  <si>
-    <r>
-      <t>Killdeer (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Charadrius vociferus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Ground and Open-Country</t>
-  </si>
-  <si>
-    <t>CHVO</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Greater Roadrunner </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(Geococcyx californianus)</t>
-    </r>
-  </si>
-  <si>
-    <t>GECA</t>
-  </si>
-  <si>
-    <r>
-      <t>Wild Turkey (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Meleagris gallopavo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>MEGA</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Ecogroup</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Pond</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>mammal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predator </t>
-  </si>
-  <si>
-    <t>PU</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>Small Herbivore</t>
-  </si>
-  <si>
-    <t>Omivore</t>
-  </si>
-  <si>
-    <t>reptile</t>
-  </si>
-  <si>
-    <t>Herbivore</t>
-  </si>
-  <si>
-    <t>Omnivore</t>
+    <t>BUIB</t>
   </si>
 </sst>
 </file>
@@ -1157,11 +1157,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1182,19 +1191,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1533,7 +1533,7 @@
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="30.08203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.08203125" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.9140625" customWidth="1"/>
     <col min="3" max="3" width="7.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
@@ -1542,30 +1542,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:9" ht="14.5" thickBot="1">
-      <c r="A2" s="20"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="16"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1586,7 +1586,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" thickTop="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1615,7 +1615,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1644,7 +1644,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -1673,7 +1673,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1702,14 +1702,14 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -1731,14 +1731,14 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D8" s="4">
         <v>41</v>
@@ -1760,14 +1760,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1789,14 +1789,14 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D10" s="4">
         <v>3</v>
@@ -1818,14 +1818,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1847,14 +1847,14 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1876,14 +1876,14 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D13" s="4">
         <v>0</v>
@@ -1905,14 +1905,14 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -1934,14 +1934,14 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="D15" s="4">
         <v>9</v>
@@ -1963,14 +1963,14 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D16" s="4">
         <v>7</v>
@@ -1992,14 +1992,14 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -2021,14 +2021,14 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D18" s="4">
         <v>0</v>
@@ -2050,14 +2050,14 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D19" s="4">
         <v>0</v>
@@ -2079,14 +2079,14 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D20" s="4">
         <v>0</v>
@@ -2108,14 +2108,14 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D21" s="4">
         <v>0</v>
@@ -2137,14 +2137,14 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D22" s="4">
         <v>0</v>
@@ -2166,14 +2166,14 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D23" s="4">
         <v>0</v>
@@ -2195,14 +2195,14 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="21" t="s">
-        <v>57</v>
+      <c r="A24" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
@@ -2224,14 +2224,14 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="21" t="s">
-        <v>59</v>
+      <c r="A25" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D25" s="4">
         <v>0</v>
@@ -2253,14 +2253,14 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="21" t="s">
-        <v>61</v>
+      <c r="A26" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D26" s="4">
         <v>0</v>
@@ -2282,14 +2282,14 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="A27" s="21" t="s">
-        <v>63</v>
+      <c r="A27" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27" s="4">
         <v>0</v>
@@ -2311,14 +2311,14 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="D28" s="4">
         <v>3</v>
@@ -2340,14 +2340,14 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="A29" s="21" t="s">
-        <v>68</v>
+      <c r="A29" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="D29" s="4">
         <v>0</v>
@@ -2369,14 +2369,14 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
-      <c r="A30" s="21" t="s">
-        <v>70</v>
+      <c r="A30" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D30" s="4">
         <v>0</v>
@@ -2398,14 +2398,14 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
-      <c r="A31" s="21" t="s">
-        <v>72</v>
+      <c r="A31" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D31" s="4">
         <v>0</v>
@@ -2427,14 +2427,14 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
-      <c r="A32" s="21" t="s">
-        <v>74</v>
+      <c r="A32" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D32" s="4">
         <v>0</v>
@@ -2456,14 +2456,14 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="15" customHeight="1">
-      <c r="A33" s="21" t="s">
-        <v>76</v>
+      <c r="A33" s="11" t="s">
+        <v>73</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D33" s="4">
         <v>0</v>
@@ -2485,14 +2485,14 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1">
-      <c r="A34" s="21" t="s">
-        <v>78</v>
+      <c r="A34" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D34" s="4">
         <v>0</v>
@@ -2514,14 +2514,14 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
-      <c r="A35" s="21" t="s">
-        <v>80</v>
+      <c r="A35" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D35" s="4">
         <v>0</v>
@@ -2543,14 +2543,14 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1">
-      <c r="A36" s="21" t="s">
-        <v>83</v>
+      <c r="A36" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D36" s="4">
         <v>3</v>
@@ -2572,14 +2572,14 @@
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" thickBot="1">
-      <c r="A37" s="22" t="s">
-        <v>85</v>
+      <c r="A37" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D37" s="9">
         <v>0</v>
@@ -2626,52 +2626,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="G1" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="2" spans="1:7" ht="14.5" thickBot="1">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" thickTop="1">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>5</v>
@@ -2685,16 +2685,16 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
@@ -2708,16 +2708,16 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -2731,16 +2731,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>5</v>
@@ -2754,16 +2754,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>6</v>
@@ -2777,16 +2777,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>7</v>
@@ -2800,16 +2800,16 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>5</v>
@@ -2823,16 +2823,16 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
@@ -2846,16 +2846,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>7</v>
@@ -2869,16 +2869,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>5</v>
@@ -2892,16 +2892,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
@@ -2915,16 +2915,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>7</v>
@@ -2938,7 +2938,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>15</v>
@@ -2947,7 +2947,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>5</v>
@@ -2961,7 +2961,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>15</v>
@@ -2970,7 +2970,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
@@ -2984,7 +2984,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>15</v>
@@ -2993,7 +2993,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>7</v>
@@ -3007,7 +3007,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>15</v>
@@ -3016,7 +3016,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>5</v>
@@ -3030,7 +3030,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>15</v>
@@ -3039,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -3053,7 +3053,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>15</v>
@@ -3062,7 +3062,7 @@
         <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>7</v>
@@ -3076,16 +3076,16 @@
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>5</v>
@@ -3099,16 +3099,16 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
@@ -3122,16 +3122,16 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>7</v>
@@ -3145,16 +3145,16 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>5</v>
@@ -3168,16 +3168,16 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
@@ -3191,16 +3191,16 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>7</v>
@@ -3214,16 +3214,16 @@
         <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>5</v>
@@ -3237,16 +3237,16 @@
         <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
@@ -3260,16 +3260,16 @@
         <v>19</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>7</v>
@@ -3283,16 +3283,16 @@
         <v>19</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>5</v>
@@ -3306,16 +3306,16 @@
         <v>19</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
@@ -3329,16 +3329,16 @@
         <v>19</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>7</v>
@@ -3349,19 +3349,19 @@
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>5</v>
@@ -3372,19 +3372,19 @@
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
@@ -3395,19 +3395,19 @@
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>7</v>
@@ -3418,19 +3418,19 @@
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>5</v>
@@ -3441,19 +3441,19 @@
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
@@ -3464,19 +3464,19 @@
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>7</v>
@@ -3487,19 +3487,19 @@
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1">
       <c r="A39" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D39" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>5</v>
@@ -3510,19 +3510,19 @@
     </row>
     <row r="40" spans="1:7" ht="15" customHeight="1">
       <c r="A40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D40" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
@@ -3533,19 +3533,19 @@
     </row>
     <row r="41" spans="1:7" ht="15" customHeight="1">
       <c r="A41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D41" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>7</v>
@@ -3556,19 +3556,19 @@
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1">
       <c r="A42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="D42" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>5</v>
@@ -3579,19 +3579,19 @@
     </row>
     <row r="43" spans="1:7" ht="15" customHeight="1">
       <c r="A43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="D43" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
@@ -3602,19 +3602,19 @@
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1">
       <c r="A44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="D44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>7</v>
@@ -3625,19 +3625,19 @@
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1">
       <c r="A45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D45" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>5</v>
@@ -3648,19 +3648,19 @@
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1">
       <c r="A46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D46" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
@@ -3671,19 +3671,19 @@
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1">
       <c r="A47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D47" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>7</v>
@@ -3694,19 +3694,19 @@
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1">
       <c r="A48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="D48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>5</v>
@@ -3717,19 +3717,19 @@
     </row>
     <row r="49" spans="1:7" ht="15" customHeight="1">
       <c r="A49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="D49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
@@ -3740,19 +3740,19 @@
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1">
       <c r="A50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="D50" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>7</v>
@@ -3763,19 +3763,19 @@
     </row>
     <row r="51" spans="1:7" ht="15" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D51" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>5</v>
@@ -3786,19 +3786,19 @@
     </row>
     <row r="52" spans="1:7" ht="15" customHeight="1">
       <c r="A52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D52" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
@@ -3809,19 +3809,19 @@
     </row>
     <row r="53" spans="1:7" ht="15" customHeight="1">
       <c r="A53" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D53" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>7</v>
@@ -3832,19 +3832,19 @@
     </row>
     <row r="54" spans="1:7" ht="15" customHeight="1">
       <c r="A54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="D54" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>5</v>
@@ -3855,19 +3855,19 @@
     </row>
     <row r="55" spans="1:7" ht="15" customHeight="1">
       <c r="A55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="D55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
@@ -3878,19 +3878,19 @@
     </row>
     <row r="56" spans="1:7" ht="15" customHeight="1">
       <c r="A56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="D56" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>7</v>
@@ -3901,19 +3901,19 @@
     </row>
     <row r="57" spans="1:7" ht="15" customHeight="1">
       <c r="A57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D57" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>5</v>
@@ -3924,19 +3924,19 @@
     </row>
     <row r="58" spans="1:7" ht="15" customHeight="1">
       <c r="A58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D58" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
@@ -3947,19 +3947,19 @@
     </row>
     <row r="59" spans="1:7" ht="15" customHeight="1">
       <c r="A59" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D59" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>7</v>
@@ -3970,19 +3970,19 @@
     </row>
     <row r="60" spans="1:7" ht="15" customHeight="1">
       <c r="A60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="D60" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>5</v>
@@ -3993,19 +3993,19 @@
     </row>
     <row r="61" spans="1:7" ht="15" customHeight="1">
       <c r="A61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="D61" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
@@ -4016,19 +4016,19 @@
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1">
       <c r="A62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="D62" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>7</v>
@@ -4039,19 +4039,19 @@
     </row>
     <row r="63" spans="1:7" ht="15" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>5</v>
@@ -4062,19 +4062,19 @@
     </row>
     <row r="64" spans="1:7" ht="15" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>6</v>
@@ -4085,19 +4085,19 @@
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>7</v>
@@ -4108,19 +4108,19 @@
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>5</v>
@@ -4131,19 +4131,19 @@
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
@@ -4154,19 +4154,19 @@
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>7</v>
@@ -4177,19 +4177,19 @@
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1">
       <c r="A69" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D69" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>5</v>
@@ -4200,19 +4200,19 @@
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1">
       <c r="A70" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D70" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>6</v>
@@ -4223,19 +4223,19 @@
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1">
       <c r="A71" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D71" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>7</v>
@@ -4246,19 +4246,19 @@
     </row>
     <row r="72" spans="1:7" ht="15" customHeight="1">
       <c r="A72" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D72" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>5</v>
@@ -4269,19 +4269,19 @@
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D73" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
@@ -4292,19 +4292,19 @@
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1">
       <c r="A74" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>7</v>
